--- a/erp-server/erp-server-wms/src/main/resources/excel/StocktakingTaskDetail.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/StocktakingTaskDetail.xlsx
@@ -54,10 +54,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{.skuName}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>可用库存</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -95,6 +91,10 @@
   </si>
   <si>
     <t>{.stocktakingUserName}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.productName}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -473,19 +473,19 @@
         <v>8</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -502,22 +502,22 @@
         <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="J2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/StocktakingTaskDetail.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/StocktakingTaskDetail.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>盘点任务单号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -95,6 +95,14 @@
   </si>
   <si>
     <t>{.productName}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>盘点方式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.stocktakingModeName}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -444,79 +452,85 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="25.625" customWidth="1"/>
-    <col min="2" max="2" width="26.125" customWidth="1"/>
-    <col min="3" max="3" width="14.875" customWidth="1"/>
-    <col min="4" max="4" width="15.625" customWidth="1"/>
-    <col min="5" max="5" width="18.125" customWidth="1"/>
-    <col min="6" max="9" width="20.625" customWidth="1"/>
-    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="1" max="2" width="25.625" customWidth="1"/>
+    <col min="3" max="3" width="26.125" customWidth="1"/>
+    <col min="4" max="4" width="14.875" customWidth="1"/>
+    <col min="5" max="5" width="15.625" customWidth="1"/>
+    <col min="6" max="6" width="18.125" customWidth="1"/>
+    <col min="7" max="10" width="20.625" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>18</v>
       </c>
     </row>
